--- a/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>80408</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-7.187</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.5142</v>
-      </c>
-      <c r="I2" t="n">
-        <v>245</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-7.187</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.5142</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>180</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-7.22621</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.43226</v>
-      </c>
-      <c r="I3" t="n">
-        <v>329</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-7.22621</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.43226</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>80392 ANDRES SALVADOR DIAZ SAGASTEGUI</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-7.227803</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.42505199999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>278</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-7.227803</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.425052</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SANTA JUANA DE LESTONNAC</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-7.224</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.4288</v>
-      </c>
-      <c r="I5" t="n">
-        <v>632</v>
-      </c>
-      <c r="J5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-7.224</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.4288</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>80382 CARLOS A. OLIVARES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-7.228072</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.42783799999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1313</v>
-      </c>
-      <c r="J6" t="n">
-        <v>63</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-7.228072</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.427838</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>80386</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-7.227</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.4315</v>
-      </c>
-      <c r="I7" t="n">
-        <v>491</v>
-      </c>
-      <c r="J7" t="n">
-        <v>29</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-7.227</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.4315</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>80388 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-7.2312</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.4164</v>
-      </c>
-      <c r="I8" t="n">
-        <v>284</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-7.2312</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.4164</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>80389</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-7.2303</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.4222</v>
-      </c>
-      <c r="I9" t="n">
-        <v>271</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-7.2303</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.4222</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>80390</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-7.23049</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.412065</v>
-      </c>
-      <c r="I10" t="n">
-        <v>281</v>
-      </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-7.23049</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.412065</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>80391 ALFREDO NOVOA CAVA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-7.2323</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.42700000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>416</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-7.2323</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.427</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>1639 / 80830 ZOILA HORA DE ROBLES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-7.2315</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.4299</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J12" t="n">
-        <v>111</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-7.2315</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.4299</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>81031</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-7.2289</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.429</v>
-      </c>
-      <c r="I13" t="n">
-        <v>281</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-7.2289</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.429</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>81560</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-7.29084</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.32308999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>244</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-7.29084</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.32309</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>CARLOS GUTIERREZ NORIEGA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-7.2224</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.4342</v>
-      </c>
-      <c r="I15" t="n">
-        <v>300</v>
-      </c>
-      <c r="J15" t="n">
-        <v>30</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-7.2224</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.4342</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>19</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-7.2259</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.4316</v>
-      </c>
-      <c r="I16" t="n">
-        <v>472</v>
-      </c>
-      <c r="J16" t="n">
-        <v>32</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-7.2259</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.4316</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>66</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-7.23245</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.41509000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>515</v>
-      </c>
-      <c r="J17" t="n">
-        <v>34</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-7.23245</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.41509</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>81558 IMELDA CAVA VARGAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-7.242666</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.399314</v>
-      </c>
-      <c r="I18" t="n">
-        <v>231</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-7.242666</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.399314</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>LA ASOCIACION</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-7.22839</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.42888000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-7.22839</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.42888</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-7.22942</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.43087</v>
-      </c>
-      <c r="I20" t="n">
-        <v>504</v>
-      </c>
-      <c r="J20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-7.22942</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.43087</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>ALECRIM</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-7.23193</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.42518</v>
-      </c>
-      <c r="I21" t="n">
-        <v>170</v>
-      </c>
-      <c r="J21" t="n">
-        <v>10</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-7.23193</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.42518</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>80401</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-7.17466</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.47993</v>
-      </c>
-      <c r="I22" t="n">
-        <v>290</v>
-      </c>
-      <c r="J22" t="n">
-        <v>19</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-7.17466</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.47993</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>80402</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-7.17186</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.48545</v>
-      </c>
-      <c r="I23" t="n">
-        <v>217</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-7.17186</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.48545</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>FRANCISCO RICCI</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-7.23199</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.42541</v>
-      </c>
-      <c r="I24" t="n">
-        <v>114</v>
-      </c>
-      <c r="J24" t="n">
-        <v>9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-7.23199</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.42541</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>259198</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80408</t>
+          <t>LA ASOCIACION</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.187</t>
+          <t>-7.22839</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.5142</t>
+          <t>-79.42888</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>258622</t>
+          <t>259235</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.22621</t>
+          <t>-7.23193</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.43226</t>
+          <t>-79.42518</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>258702</t>
+          <t>258882</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80392 ANDRES SALVADOR DIAZ SAGASTEGUI</t>
+          <t>1639 / 80830 ZOILA HORA DE ROBLES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.227803</t>
+          <t>-7.2315</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.425052</t>
+          <t>-79.4299</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>258764</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANTA JUANA DE LESTONNAC</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.224</t>
+          <t>-7.187</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.4288</t>
+          <t>-79.5142</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>258783</t>
+          <t>258622</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>80382 CARLOS A. OLIVARES</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.228072</t>
+          <t>-7.22621</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.427838</t>
+          <t>-79.43226</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>258797</t>
+          <t>258702</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80386</t>
+          <t>80392 ANDRES SALVADOR DIAZ SAGASTEGUI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.227</t>
+          <t>-7.227803</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.4315</t>
+          <t>-79.425052</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>258801</t>
+          <t>258943</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80388 DIVINO MAESTRO</t>
+          <t>81560</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.2312</t>
+          <t>-7.29084</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.4164</t>
+          <t>-79.32309</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>258815</t>
+          <t>258801</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80389</t>
+          <t>80388 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.2303</t>
+          <t>-7.2312</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.4222</t>
+          <t>-79.4164</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>258839</t>
+          <t>258924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80391 ALFREDO NOVOA CAVA</t>
+          <t>81031</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.2323</t>
+          <t>-7.2289</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.427</t>
+          <t>-79.429</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,42 +1121,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>259117</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1639 / 80830 ZOILA HORA DE ROBLES</t>
+          <t>81558 IMELDA CAVA VARGAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.2315</t>
+          <t>-7.242666</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.4299</t>
+          <t>-79.399314</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,27 +1183,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>258924</t>
+          <t>259424</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>80402</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.2289</t>
+          <t>-7.17186</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.429</t>
+          <t>-79.48545</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>258943</t>
+          <t>258815</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>80389</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.29084</t>
+          <t>-7.2303</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.32309</t>
+          <t>-79.4222</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>259037</t>
+          <t>258839</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CARLOS GUTIERREZ NORIEGA</t>
+          <t>80391 ALFREDO NOVOA CAVA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.2224</t>
+          <t>-7.2323</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.4342</t>
+          <t>-79.427</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>259042</t>
+          <t>259419</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>80401</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-7.17466</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.47993</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-7.2259</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-79.4316</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>259056</t>
+          <t>259202</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.23245</t>
+          <t>-7.22942</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.41509</t>
+          <t>-79.43087</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,42 +1493,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>259117</t>
+          <t>258797</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>81558 IMELDA CAVA VARGAS</t>
+          <t>80386</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.242666</t>
+          <t>-7.227</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.399314</t>
+          <t>-79.4315</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,42 +1555,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>259198</t>
+          <t>258764</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LA ASOCIACION</t>
+          <t>SANTA JUANA DE LESTONNAC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.22839</t>
+          <t>-7.224</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.42888</t>
+          <t>-79.4288</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>259202</t>
+          <t>259037</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>CARLOS GUTIERREZ NORIEGA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.22942</t>
+          <t>-7.2224</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.43087</t>
+          <t>-79.4342</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>259235</t>
+          <t>259042</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.23193</t>
+          <t>-7.2259</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.42518</t>
+          <t>-79.4316</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>472</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>259419</t>
+          <t>259056</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.17466</t>
+          <t>-7.23245</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.47993</t>
+          <t>-79.41509</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>259424</t>
+          <t>258783</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>80382 CARLOS A. OLIVARES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.17186</t>
+          <t>-7.228072</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.48545</t>
+          <t>-79.427838</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>259198</t>
+          <t>630565</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LA ASOCIACION</t>
+          <t>FRANCISCO RICCI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-7.22839</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.42888</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-7.23199</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-79.42541</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>259235</t>
+          <t>259424</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALECRIM</t>
+          <t>80402</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.23193</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.42518</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>-7.17186</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.48545</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>259419</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1639 / 80830 ZOILA HORA DE ROBLES</t>
+          <t>80401</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-7.2315</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.4299</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>-7.17466</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>-79.47993</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>259235</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80408</t>
+          <t>ALECRIM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.187</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.5142</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-7.23193</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.42518</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>258622</t>
+          <t>259202</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.22621</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.43226</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-7.22942</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.43087</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>258702</t>
+          <t>259198</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80392 ANDRES SALVADOR DIAZ SAGASTEGUI</t>
+          <t>LA ASOCIACION</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.227803</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.425052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-7.22839</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.42888</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,42 +873,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>258943</t>
+          <t>259117</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>81558 IMELDA CAVA VARGAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.29084</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.32309</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-7.242666</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.399314</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>258801</t>
+          <t>259056</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80388 DIVINO MAESTRO</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-7.2312</t>
+          <t>515</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.4164</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-7.23245</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.41509</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>258820</t>
+          <t>259042</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80390</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-7.23049</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.412065</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-7.2259</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.4316</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>258924</t>
+          <t>259037</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>CARLOS GUTIERREZ NORIEGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-7.2289</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.429</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>-7.2224</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.4342</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,42 +1121,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>259117</t>
+          <t>258943</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>81558 IMELDA CAVA VARGAS</t>
+          <t>81560</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.242666</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.399314</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-7.29084</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.32309</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>259424</t>
+          <t>258924</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>81031</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.17186</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.48545</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-7.2289</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.429</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>258815</t>
+          <t>258882</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>80389</t>
+          <t>1639 / 80830 ZOILA HORA DE ROBLES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-7.2303</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.4222</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-7.2315</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.4299</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>-7.2323</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-79.427</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>259419</t>
+          <t>258820</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>80390</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.17466</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.47993</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-7.23049</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.412065</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>259202</t>
+          <t>258815</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>80389</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-7.22942</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.43087</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-7.2303</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.4222</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>258797</t>
+          <t>258801</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80386</t>
+          <t>80388 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.227</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.4315</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-7.2312</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.4164</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>258764</t>
+          <t>258797</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SANTA JUANA DE LESTONNAC</t>
+          <t>80386</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.224</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.4288</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>-7.227</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.4315</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,42 +1617,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>259037</t>
+          <t>258783</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CARLOS GUTIERREZ NORIEGA</t>
+          <t>80382 CARLOS A. OLIVARES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.2224</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.4342</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-7.228072</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.427838</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>259042</t>
+          <t>258764</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>SANTA JUANA DE LESTONNAC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-7.2259</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.4316</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>-7.224</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-79.4288</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>259056</t>
+          <t>258702</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>80392 ANDRES SALVADOR DIAZ SAGASTEGUI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.23245</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.41509</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>-7.227803</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.425052</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>258783</t>
+          <t>258622</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80382 CARLOS A. OLIVARES</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-7.228072</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.427838</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>-7.22621</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-79.43226</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>630565</t>
+          <t>023025</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FRANCISCO RICCI</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.23199</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.42541</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-7.187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.5142</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-CHEPEN-CHEPEN.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
